--- a/Documentation/Week 7/Booked Hours/Booked_Hours_Dhava.xlsx
+++ b/Documentation/Week 7/Booked Hours/Booked_Hours_Dhava.xlsx
@@ -5,12 +5,12 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wikha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 7/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE39FE2D-5460-44F6-8BD4-1C6E8CADE08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BE39FE2D-5460-44F6-8BD4-1C6E8CADE08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CEE642B-67C5-4988-B960-754CF4B496EA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,19 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -444,6 +457,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -906,7 +923,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D6" s="4">
-        <v>44746</v>
+        <v>44777</v>
       </c>
       <c r="E6" s="5">
         <v>0.45833333333333331</v>
@@ -923,7 +940,7 @@
       </c>
       <c r="I6" s="1">
         <f t="shared" si="1"/>
-        <v>-742.99999999988358</v>
+        <v>1.0000000001164153</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -937,7 +954,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="D7" s="4">
-        <v>44746</v>
+        <v>44777</v>
       </c>
       <c r="E7" s="5">
         <v>0.58333333333333337</v>
@@ -954,7 +971,7 @@
       </c>
       <c r="I7" s="1">
         <f t="shared" si="1"/>
-        <v>-742.99999999988358</v>
+        <v>1.0000000001164153</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
